--- a/EG1B.xlsx
+++ b/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="61">
   <si>
     <t/>
   </si>
   <si>
-    <t>20139538</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT 105G</t>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -31,187 +31,169 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10035852</t>
+  </si>
+  <si>
+    <t>BIHUNKU GRG SPCL 60G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20123088</t>
+  </si>
+  <si>
+    <t>SEDAAP KCP MNS 720ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20126424</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20116112</t>
+  </si>
+  <si>
+    <t>MAXICORN BBQ 140G</t>
+  </si>
+  <si>
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20000516</t>
-  </si>
-  <si>
-    <t>KUSUKA KRPK BBQ 180</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20125580</t>
-  </si>
-  <si>
-    <t>JAPOTA NPS PDS 68G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20045784</t>
-  </si>
-  <si>
-    <t>OISHI SPNG/C CHO 100</t>
-  </si>
-  <si>
-    <t>20047335</t>
-  </si>
-  <si>
-    <t>OISHI SPNG STRW 100G</t>
-  </si>
-  <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 68</t>
-  </si>
-  <si>
-    <t>20055205</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 62G</t>
-  </si>
-  <si>
-    <t>20132864</t>
-  </si>
-  <si>
-    <t>TIC TAC MIE GORENG80</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 47GR</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW 45</t>
-  </si>
-  <si>
-    <t>20095021</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CKLT 76G</t>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
+  </si>
+  <si>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
+  </si>
+  <si>
+    <t>10000341</t>
+  </si>
+  <si>
+    <t>DUA KELINCI KCG 370G</t>
+  </si>
+  <si>
+    <t>20115362</t>
+  </si>
+  <si>
+    <t>CHUBA KRP BALADO 125</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 140</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20113383</t>
-  </si>
-  <si>
-    <t>ROMA KLPA FRSH 6'S</t>
-  </si>
-  <si>
-    <t>10003844</t>
-  </si>
-  <si>
-    <t>INACO JELLY MINI 15S</t>
-  </si>
-  <si>
-    <t>20128291</t>
-  </si>
-  <si>
-    <t>IDM KCG ALMD MADU 65</t>
+    <t>20122289</t>
+  </si>
+  <si>
+    <t>BONCABE MK LV2 NC135</t>
+  </si>
+  <si>
+    <t>20056977</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA BWG 95</t>
+  </si>
+  <si>
+    <t>20089490</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA PDS 90G</t>
+  </si>
+  <si>
+    <t>20139132</t>
+  </si>
+  <si>
+    <t>GRUDA RS.MAX B&amp;S 80G</t>
+  </si>
+  <si>
+    <t>20092875</t>
+  </si>
+  <si>
+    <t>GRUDA PILUS MI GR 80</t>
+  </si>
+  <si>
+    <t>20127483</t>
+  </si>
+  <si>
+    <t>GRUDA PILUS RDNG 80</t>
+  </si>
+  <si>
+    <t>20071797</t>
+  </si>
+  <si>
+    <t>NEXTAR PINEAPPLE 8'S</t>
+  </si>
+  <si>
+    <t>20138465</t>
+  </si>
+  <si>
+    <t>NEXTAR STRAWBRY 90G</t>
+  </si>
+  <si>
+    <t>20124895</t>
+  </si>
+  <si>
+    <t>G/T COKIES CHOCDIP71</t>
+  </si>
+  <si>
+    <t>10003324</t>
+  </si>
+  <si>
+    <t>MONDE GENJIE PIE 70G</t>
+  </si>
+  <si>
+    <t>10008579</t>
+  </si>
+  <si>
+    <t>DELFI MINIS BLK.VN70</t>
+  </si>
+  <si>
+    <t>10008580</t>
+  </si>
+  <si>
+    <t>DELFI MINIS CHOCO 70</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>20026676</t>
-  </si>
-  <si>
-    <t>INDOMARET GARAM 500G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>20134353</t>
-  </si>
-  <si>
-    <t>IDM S/B NNS&amp;MRKSA220</t>
-  </si>
-  <si>
-    <t>20134354</t>
-  </si>
-  <si>
-    <t>IDM SARI BH NANAS220</t>
-  </si>
-  <si>
-    <t>20087713</t>
-  </si>
-  <si>
-    <t>IDM NDL AYM PDS 90G</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>20136102</t>
-  </si>
-  <si>
-    <t>IDM SOES STROBERI80G</t>
-  </si>
-  <si>
-    <t>20042632</t>
-  </si>
-  <si>
-    <t>IDM KCG ATOM PDS 140</t>
-  </si>
-  <si>
-    <t>20136516</t>
-  </si>
-  <si>
-    <t>IDM KC ATM CB IJO120</t>
   </si>
 </sst>
 </file>
@@ -604,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -671,15 +653,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -688,18 +670,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -708,27 +690,27 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -736,10 +718,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -748,18 +730,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -768,10 +750,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -788,10 +770,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -808,24 +790,24 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -836,22 +818,22 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -865,10 +847,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>35</v>
@@ -885,13 +867,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -905,13 +887,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -925,110 +907,110 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1036,59 +1018,59 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1096,61 +1078,21 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="1" t="s">
         <v>5</v>
       </c>
     </row>
